--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/09 Septiembre/Liquidacióncvs -septiembre/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4981" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495E48B9-0B84-4500-851B-3859EA01DA4A}"/>
+  <xr:revisionPtr revIDLastSave="5011" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B6BF06F-1F55-4443-9E6E-E65E5752DE22}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -38150,7 +38150,9 @@
       <c r="F1444" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G1444"/>
+      <c r="G1444">
+        <v>20933800</v>
+      </c>
     </row>
     <row r="1445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1445" s="2">
@@ -38172,7 +38174,7 @@
         <v>63</v>
       </c>
       <c r="G1445">
-        <v>0</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="1446" spans="1:8" x14ac:dyDescent="0.25">
@@ -38186,7 +38188,7 @@
         <v>63</v>
       </c>
       <c r="G1446">
-        <v>0</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1447" spans="1:8" x14ac:dyDescent="0.25">
@@ -38200,7 +38202,7 @@
         <v>63</v>
       </c>
       <c r="G1447">
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="1448" spans="1:8" x14ac:dyDescent="0.25">
@@ -38228,7 +38230,7 @@
         <v>63</v>
       </c>
       <c r="G1449">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1450" spans="1:8" x14ac:dyDescent="0.25">
@@ -38242,7 +38244,7 @@
         <v>63</v>
       </c>
       <c r="G1450">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1451" spans="1:8" x14ac:dyDescent="0.25">
@@ -38256,7 +38258,7 @@
         <v>63</v>
       </c>
       <c r="G1451">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -38270,7 +38272,7 @@
         <v>63</v>
       </c>
       <c r="G1452">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -38284,7 +38286,7 @@
         <v>63</v>
       </c>
       <c r="G1453">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.25">
@@ -38298,7 +38300,7 @@
         <v>63</v>
       </c>
       <c r="G1454">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1455" spans="1:8" x14ac:dyDescent="0.25">
@@ -38312,7 +38314,7 @@
         <v>63</v>
       </c>
       <c r="G1455">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="1456" spans="1:8" x14ac:dyDescent="0.25">
@@ -38326,7 +38328,7 @@
         <v>63</v>
       </c>
       <c r="G1456">
-        <v>0</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1457" spans="1:7" x14ac:dyDescent="0.25">
@@ -38340,7 +38342,7 @@
         <v>63</v>
       </c>
       <c r="G1457">
-        <v>0</v>
+        <v>211</v>
       </c>
     </row>
     <row r="1458" spans="1:7" x14ac:dyDescent="0.25">
@@ -38354,7 +38356,7 @@
         <v>63</v>
       </c>
       <c r="G1458">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1459" spans="1:7" x14ac:dyDescent="0.25">
@@ -38368,7 +38370,7 @@
         <v>63</v>
       </c>
       <c r="G1459">
-        <v>0</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1460" spans="1:7" x14ac:dyDescent="0.25">
@@ -38382,7 +38384,7 @@
         <v>63</v>
       </c>
       <c r="G1460">
-        <v>0</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1461" spans="1:7" x14ac:dyDescent="0.25">
@@ -38396,7 +38398,7 @@
         <v>63</v>
       </c>
       <c r="G1461">
-        <v>0</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1462" spans="1:7" x14ac:dyDescent="0.25">
@@ -38410,7 +38412,7 @@
         <v>63</v>
       </c>
       <c r="G1462">
-        <v>0</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1463" spans="1:7" x14ac:dyDescent="0.25">
@@ -38424,7 +38426,7 @@
         <v>63</v>
       </c>
       <c r="G1463">
-        <v>0</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1464" spans="1:7" x14ac:dyDescent="0.25">
@@ -38438,7 +38440,7 @@
         <v>63</v>
       </c>
       <c r="G1464">
-        <v>0</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1465" spans="1:7" x14ac:dyDescent="0.25">
@@ -38452,7 +38454,7 @@
         <v>63</v>
       </c>
       <c r="G1465">
-        <v>0</v>
+        <v>645</v>
       </c>
     </row>
     <row r="1466" spans="1:7" x14ac:dyDescent="0.25">
@@ -38466,7 +38468,7 @@
         <v>63</v>
       </c>
       <c r="G1466">
-        <v>0</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1467" spans="1:7" x14ac:dyDescent="0.25">
@@ -38480,7 +38482,7 @@
         <v>63</v>
       </c>
       <c r="G1467">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1468" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/09 Septiembre/Liquidacióncvs -septiembre/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5198" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67428374-7BE2-4A46-A50B-89C1FCC762D9}"/>
+  <xr:revisionPtr revIDLastSave="5201" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D719B9D9-1913-415A-9A94-05D7DCCDEDB4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10106" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10110" uniqueCount="100">
   <si>
     <t>Sucursal</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>Lider Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
   </si>
 </sst>
 </file>
@@ -65913,7 +65916,7 @@
         <v>625000</v>
       </c>
     </row>
-    <row r="2545" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2545" s="2">
         <v>46267</v>
       </c>
@@ -65936,7 +65939,7 @@
         <v>1310900</v>
       </c>
     </row>
-    <row r="2546" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2546" s="2">
         <v>46272</v>
       </c>
@@ -65959,7 +65962,7 @@
         <v>648000</v>
       </c>
     </row>
-    <row r="2547" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2547" s="2">
         <v>46266</v>
       </c>
@@ -65982,7 +65985,7 @@
         <v>996000</v>
       </c>
     </row>
-    <row r="2548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2548" s="2">
         <v>46276</v>
       </c>
@@ -66005,7 +66008,7 @@
         <v>613000</v>
       </c>
     </row>
-    <row r="2549" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2549" s="2">
         <v>46269</v>
       </c>
@@ -66028,7 +66031,7 @@
         <v>654000</v>
       </c>
     </row>
-    <row r="2550" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2550" s="2">
         <v>46274</v>
       </c>
@@ -66051,7 +66054,7 @@
         <v>610000</v>
       </c>
     </row>
-    <row r="2551" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2551" s="2">
         <v>46274</v>
       </c>
@@ -66074,21 +66077,40 @@
         <v>1026000</v>
       </c>
     </row>
-    <row r="2552" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2552" s="2"/>
-      <c r="C2552" s="3"/>
-      <c r="D2552" s="3"/>
-      <c r="E2552" s="3"/>
-      <c r="G2552"/>
-    </row>
-    <row r="2553" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2552" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2552" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B2552" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2552">
+        <v>10171674991</v>
+      </c>
+      <c r="D2552" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2552" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2552" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2552">
+        <v>1</v>
+      </c>
+      <c r="H2552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2553" s="2"/>
       <c r="C2553" s="3"/>
       <c r="D2553" s="3"/>
       <c r="E2553" s="3"/>
       <c r="G2553"/>
     </row>
-    <row r="2554" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2554" s="2"/>
       <c r="B2554" s="3"/>
       <c r="C2554" s="3"/>
@@ -66096,14 +66118,14 @@
       <c r="E2554" s="3"/>
       <c r="G2554"/>
     </row>
-    <row r="2555" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2555" s="2"/>
       <c r="C2555" s="3"/>
       <c r="D2555" s="3"/>
       <c r="E2555" s="3"/>
       <c r="G2555"/>
     </row>
-    <row r="2556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2556" s="2"/>
       <c r="B2556" s="3"/>
       <c r="C2556" s="3"/>
@@ -66111,14 +66133,14 @@
       <c r="E2556" s="3"/>
       <c r="G2556"/>
     </row>
-    <row r="2557" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2557" s="2"/>
       <c r="C2557" s="3"/>
       <c r="D2557" s="3"/>
       <c r="E2557" s="3"/>
       <c r="G2557"/>
     </row>
-    <row r="2558" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2558" s="2"/>
       <c r="B2558" s="3"/>
       <c r="C2558" s="3"/>
@@ -66126,14 +66148,14 @@
       <c r="E2558" s="3"/>
       <c r="G2558"/>
     </row>
-    <row r="2559" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2559" s="2"/>
       <c r="C2559" s="3"/>
       <c r="D2559" s="3"/>
       <c r="E2559" s="3"/>
       <c r="G2559"/>
     </row>
-    <row r="2560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2560" s="2"/>
       <c r="B2560" s="3"/>
       <c r="C2560" s="3"/>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/09 Septiembre/Liquidacióncvs -septiembre/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5201" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D719B9D9-1913-415A-9A94-05D7DCCDEDB4}"/>
+  <xr:revisionPtr revIDLastSave="5225" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F961BF0C-ED50-46A1-9860-449AC4094DE9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -64256,7 +64256,7 @@
         <v>63</v>
       </c>
       <c r="G2452">
-        <v>6733</v>
+        <v>10572</v>
       </c>
     </row>
     <row r="2453" spans="1:8" x14ac:dyDescent="0.25">
@@ -64270,7 +64270,7 @@
         <v>63</v>
       </c>
       <c r="G2453">
-        <v>692</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="2454" spans="1:8" x14ac:dyDescent="0.25">
@@ -64284,7 +64284,7 @@
         <v>63</v>
       </c>
       <c r="G2454">
-        <v>448</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2455" spans="1:8" x14ac:dyDescent="0.25">
@@ -64312,7 +64312,7 @@
         <v>63</v>
       </c>
       <c r="G2456">
-        <v>259</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2457" spans="1:8" x14ac:dyDescent="0.25">
@@ -64340,7 +64340,7 @@
         <v>63</v>
       </c>
       <c r="G2458">
-        <v>245</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2459" spans="1:8" x14ac:dyDescent="0.25">
@@ -64354,7 +64354,7 @@
         <v>63</v>
       </c>
       <c r="G2459">
-        <v>209</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2460" spans="1:8" x14ac:dyDescent="0.25">
@@ -64368,7 +64368,7 @@
         <v>63</v>
       </c>
       <c r="G2460">
-        <v>459</v>
+        <v>701</v>
       </c>
     </row>
     <row r="2461" spans="1:8" x14ac:dyDescent="0.25">
@@ -64382,7 +64382,7 @@
         <v>63</v>
       </c>
       <c r="G2461">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2462" spans="1:8" x14ac:dyDescent="0.25">
@@ -64396,7 +64396,7 @@
         <v>63</v>
       </c>
       <c r="G2462">
-        <v>295</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2463" spans="1:8" x14ac:dyDescent="0.25">
@@ -64410,7 +64410,7 @@
         <v>63</v>
       </c>
       <c r="G2463">
-        <v>293</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2464" spans="1:8" x14ac:dyDescent="0.25">
@@ -64424,7 +64424,7 @@
         <v>63</v>
       </c>
       <c r="G2464">
-        <v>211</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2465" spans="1:7" x14ac:dyDescent="0.25">
@@ -64438,7 +64438,7 @@
         <v>63</v>
       </c>
       <c r="G2465">
-        <v>84</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2466" spans="1:7" x14ac:dyDescent="0.25">
@@ -64452,7 +64452,7 @@
         <v>63</v>
       </c>
       <c r="G2466">
-        <v>187</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2467" spans="1:7" x14ac:dyDescent="0.25">
@@ -64466,7 +64466,7 @@
         <v>63</v>
       </c>
       <c r="G2467">
-        <v>289</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2468" spans="1:7" x14ac:dyDescent="0.25">
@@ -64480,7 +64480,7 @@
         <v>63</v>
       </c>
       <c r="G2468">
-        <v>572</v>
+        <v>940</v>
       </c>
     </row>
     <row r="2469" spans="1:7" x14ac:dyDescent="0.25">
@@ -64494,7 +64494,7 @@
         <v>63</v>
       </c>
       <c r="G2469">
-        <v>435</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2470" spans="1:7" x14ac:dyDescent="0.25">
@@ -64508,7 +64508,7 @@
         <v>63</v>
       </c>
       <c r="G2470">
-        <v>269</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2471" spans="1:7" x14ac:dyDescent="0.25">
@@ -64522,7 +64522,7 @@
         <v>63</v>
       </c>
       <c r="G2471">
-        <v>358</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2472" spans="1:7" x14ac:dyDescent="0.25">
@@ -64536,7 +64536,7 @@
         <v>63</v>
       </c>
       <c r="G2472">
-        <v>746</v>
+        <v>975</v>
       </c>
     </row>
     <row r="2473" spans="1:7" x14ac:dyDescent="0.25">
@@ -64550,7 +64550,7 @@
         <v>63</v>
       </c>
       <c r="G2473">
-        <v>183</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2474" spans="1:7" x14ac:dyDescent="0.25">
@@ -64564,7 +64564,7 @@
         <v>63</v>
       </c>
       <c r="G2474">
-        <v>345</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2475" spans="1:7" x14ac:dyDescent="0.25">
